--- a/demo-excel/04-Proyeksi-Arus-Kas-13-Minggu-demo.xlsx
+++ b/demo-excel/04-Proyeksi-Arus-Kas-13-Minggu-demo.xlsx
@@ -362,7 +362,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Saldo Akhir vs Saldo Minimum (Rp)</a:t>
+              <a:t>Saldo Akhir vs Saldo Minimum (Rp juta)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -380,7 +380,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="0EA5A4"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -402,6 +405,7 @@
               <f>'ARUS_KAS'!$B$22:$I$22</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
@@ -412,7 +416,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2563EB"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -434,6 +441,7 @@
               <f>'ARUS_KAS'!$B$23:$I$23</f>
             </numRef>
           </val>
+          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -443,6 +451,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -454,15 +463,26 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="E3E8F1"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="#,##0,," sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -479,7 +499,7 @@
       <row>26</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="3060000"/>
+    <ext cx="5760000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>

--- a/demo-excel/04-Proyeksi-Arus-Kas-13-Minggu-demo.xlsx
+++ b/demo-excel/04-Proyeksi-Arus-Kas-13-Minggu-demo.xlsx
@@ -11,6 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARAMETER" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_BASE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ARUS_KAS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-SKENARIO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FULL-DASHBOARD" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
     <numFmt numFmtId="166" formatCode="dd-mmm-yyyy"/>
     <numFmt numFmtId="167" formatCode="dd-mmm"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,6 +110,29 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B1A30"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0033445C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E8449"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -173,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -225,6 +250,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2518,4 +2549,136 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>SKENARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Perbandingan saldo kas tiga skenario (Base, Optimis, Pesimis), saldo terendah, dan minggu kritis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C0392B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="33" t="inlineStr">
+        <is>
+          <t>Fitur Versi Lengkap</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="B5" s="35" t="inlineStr">
+        <is>
+          <t>Indikator utama: saldo terendah, runway, jumlah minggu waspada/defisit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>• Sheet ini hanya tersedia di versi lengkap, lengkap dengan rumus dan grafik yang bekerja dari data Anda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>• Kapasitas data versi lengkap jauh lebih besar dibanding demo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>• Pesan versi lengkap lewat WhatsApp 089623291732.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>